--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N90_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N90_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.39203165094597</v>
+        <v>5.426205143278721</v>
       </c>
       <c r="D2" t="n">
-        <v>42.86639728801723</v>
+        <v>6.9657895593028</v>
       </c>
       <c r="E2" t="n">
-        <v>11.86521150733879</v>
+        <v>1.928096869942554</v>
       </c>
       <c r="F2" t="n">
-        <v>11.95106663399992</v>
+        <v>1.942048328024986</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.00411757101218</v>
+        <v>7.63816910528948</v>
       </c>
       <c r="D3" t="n">
-        <v>44.45901882050295</v>
+        <v>7.22459055833173</v>
       </c>
       <c r="E3" t="n">
-        <v>11.86521150733879</v>
+        <v>1.928096869942554</v>
       </c>
       <c r="F3" t="n">
-        <v>11.95106663399992</v>
+        <v>1.942048328024986</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>17.23988689599422</v>
+        <v>2.801481620599061</v>
       </c>
       <c r="D4" t="n">
-        <v>35.41430425114022</v>
+        <v>5.754824440810286</v>
       </c>
       <c r="E4" t="n">
-        <v>11.86521150733879</v>
+        <v>1.928096869942554</v>
       </c>
       <c r="F4" t="n">
-        <v>11.95106663399992</v>
+        <v>1.942048328024986</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>5.089741025881255</v>
+        <v>0.827082916705704</v>
       </c>
       <c r="D5" t="n">
-        <v>22.45902140254057</v>
+        <v>3.649590977912843</v>
       </c>
       <c r="E5" t="n">
-        <v>11.86521150733879</v>
+        <v>1.928096869942554</v>
       </c>
       <c r="F5" t="n">
-        <v>11.95106663399992</v>
+        <v>1.942048328024986</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.74017815046774</v>
+        <v>5.157778949451008</v>
       </c>
       <c r="D6" t="n">
-        <v>28.80450134043498</v>
+        <v>4.680731467820684</v>
       </c>
       <c r="E6" t="n">
-        <v>11.86521150733879</v>
+        <v>1.928096869942554</v>
       </c>
       <c r="F6" t="n">
-        <v>11.95106663399992</v>
+        <v>1.942048328024986</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>10.64618490963434</v>
+        <v>1.73000504781558</v>
       </c>
       <c r="D7" t="n">
-        <v>10.64371617487239</v>
+        <v>1.729603878416764</v>
       </c>
       <c r="E7" t="n">
-        <v>11.86521150733879</v>
+        <v>1.928096869942554</v>
       </c>
       <c r="F7" t="n">
-        <v>11.95106663399992</v>
+        <v>1.942048328024986</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>26.88285626901303</v>
+        <v>4.368464143714617</v>
       </c>
       <c r="D8" t="n">
-        <v>21.81571453418367</v>
+        <v>3.545053611804847</v>
       </c>
       <c r="E8" t="n">
-        <v>11.86521150733879</v>
+        <v>1.928096869942554</v>
       </c>
       <c r="F8" t="n">
-        <v>11.95106663399992</v>
+        <v>1.942048328024986</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>11.83808044625703</v>
+        <v>1.923688072516768</v>
       </c>
       <c r="D9" t="n">
-        <v>11.98866202429523</v>
+        <v>1.948157578947975</v>
       </c>
       <c r="E9" t="n">
-        <v>11.86521150733879</v>
+        <v>1.928096869942554</v>
       </c>
       <c r="F9" t="n">
-        <v>11.95106663399992</v>
+        <v>1.942048328024986</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>13.96795189009694</v>
+        <v>2.269792182140752</v>
       </c>
       <c r="D10" t="n">
-        <v>20.06338954298978</v>
+        <v>3.260300800735839</v>
       </c>
       <c r="E10" t="n">
-        <v>11.86521150733879</v>
+        <v>1.928096869942554</v>
       </c>
       <c r="F10" t="n">
-        <v>11.95106663399992</v>
+        <v>1.942048328024986</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>6.460216370599489</v>
+        <v>1.049785160222417</v>
       </c>
       <c r="D11" t="n">
-        <v>14.65116274130702</v>
+        <v>2.38081394546239</v>
       </c>
       <c r="E11" t="n">
-        <v>11.86521150733879</v>
+        <v>1.928096869942554</v>
       </c>
       <c r="F11" t="n">
-        <v>11.95106663399992</v>
+        <v>1.942048328024986</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>23.38272692443129</v>
+        <v>3.799693125220085</v>
       </c>
       <c r="D12" t="n">
-        <v>15.50073439698458</v>
+        <v>2.518869339509994</v>
       </c>
       <c r="E12" t="n">
-        <v>11.86521150733879</v>
+        <v>1.928096869942554</v>
       </c>
       <c r="F12" t="n">
-        <v>11.95106663399992</v>
+        <v>1.942048328024986</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>30.68296668258212</v>
+        <v>4.985982085919594</v>
       </c>
       <c r="D13" t="n">
-        <v>14.19563835095755</v>
+        <v>2.306791232030602</v>
       </c>
       <c r="E13" t="n">
-        <v>11.86521150733879</v>
+        <v>1.928096869942554</v>
       </c>
       <c r="F13" t="n">
-        <v>11.95106663399992</v>
+        <v>1.942048328024986</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>17.47513952447011</v>
+        <v>2.839710172726392</v>
       </c>
       <c r="D14" t="n">
-        <v>22.70999117422788</v>
+        <v>3.690373565812031</v>
       </c>
       <c r="E14" t="n">
-        <v>11.86521150733879</v>
+        <v>1.928096869942554</v>
       </c>
       <c r="F14" t="n">
-        <v>11.95106663399992</v>
+        <v>1.942048328024986</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>32.7557359855291</v>
+        <v>5.322807097648479</v>
       </c>
       <c r="D15" t="n">
-        <v>33.59133992431036</v>
+        <v>5.458592737700434</v>
       </c>
       <c r="E15" t="n">
-        <v>11.86521150733879</v>
+        <v>1.928096869942554</v>
       </c>
       <c r="F15" t="n">
-        <v>11.95106663399992</v>
+        <v>1.942048328024986</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>24.4040557770454</v>
+        <v>3.965659063769877</v>
       </c>
       <c r="D16" t="n">
-        <v>27.66724998899683</v>
+        <v>4.495928123211986</v>
       </c>
       <c r="E16" t="n">
-        <v>11.86521150733879</v>
+        <v>1.928096869942554</v>
       </c>
       <c r="F16" t="n">
-        <v>11.95106663399992</v>
+        <v>1.942048328024986</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>31.40031785273923</v>
+        <v>5.102551651070125</v>
       </c>
       <c r="D17" t="n">
-        <v>32.20423469758978</v>
+        <v>5.23318813835834</v>
       </c>
       <c r="E17" t="n">
-        <v>11.86521150733879</v>
+        <v>1.928096869942554</v>
       </c>
       <c r="F17" t="n">
-        <v>11.95106663399992</v>
+        <v>1.942048328024986</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34.80880296346467</v>
+        <v>5.656430481563009</v>
       </c>
       <c r="D18" t="n">
-        <v>37.94740338337057</v>
+        <v>6.166453049797718</v>
       </c>
       <c r="E18" t="n">
-        <v>11.86521150733879</v>
+        <v>1.928096869942554</v>
       </c>
       <c r="F18" t="n">
-        <v>11.95106663399992</v>
+        <v>1.942048328024986</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>12.16798131643884</v>
+        <v>1.977296963921312</v>
       </c>
       <c r="D19" t="n">
-        <v>17.00772238466914</v>
+        <v>2.763754887508735</v>
       </c>
       <c r="E19" t="n">
-        <v>11.86521150733879</v>
+        <v>1.928096869942554</v>
       </c>
       <c r="F19" t="n">
-        <v>11.95106663399992</v>
+        <v>1.942048328024986</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>43.01902900956737</v>
+        <v>6.990592214054698</v>
       </c>
       <c r="D20" t="n">
-        <v>43.67899880346693</v>
+        <v>7.097837305563377</v>
       </c>
       <c r="E20" t="n">
-        <v>11.86521150733879</v>
+        <v>1.928096869942554</v>
       </c>
       <c r="F20" t="n">
-        <v>11.95106663399992</v>
+        <v>1.942048328024986</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>18.08031077497063</v>
+        <v>2.938050500932728</v>
       </c>
       <c r="D21" t="n">
-        <v>5.399343390887453</v>
+        <v>0.8773933010192112</v>
       </c>
       <c r="E21" t="n">
-        <v>11.86521150733879</v>
+        <v>1.928096869942554</v>
       </c>
       <c r="F21" t="n">
-        <v>11.95106663399992</v>
+        <v>1.942048328024986</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>14.16332748679627</v>
+        <v>2.301540716604394</v>
       </c>
       <c r="D22" t="n">
-        <v>14.83814728050502</v>
+        <v>2.411198933082065</v>
       </c>
       <c r="E22" t="n">
-        <v>11.86521150733879</v>
+        <v>1.928096869942554</v>
       </c>
       <c r="F22" t="n">
-        <v>11.95106663399992</v>
+        <v>1.942048328024986</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>4.900825408956074</v>
+        <v>0.796384128955362</v>
       </c>
       <c r="D23" t="n">
-        <v>4.515284659924185</v>
+        <v>0.7337337572376801</v>
       </c>
       <c r="E23" t="n">
-        <v>11.86521150733879</v>
+        <v>1.928096869942554</v>
       </c>
       <c r="F23" t="n">
-        <v>11.95106663399992</v>
+        <v>1.942048328024986</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
